--- a/2026-06/R8祭礼予算・進行表.xlsx
+++ b/2026-06/R8祭礼予算・進行表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyWorks\komatest\2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D64530-707E-4C1F-9FD6-4D0F38B2F519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2810D8-5F57-42E7-B973-900053979827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="4344" windowWidth="22344" windowHeight="20136" tabRatio="807" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17652" yWindow="9276" windowWidth="27480" windowHeight="14976" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="①宵宮祭rev.A" sheetId="29" r:id="rId1"/>
@@ -102,6 +102,46 @@
         </r>
       </text>
     </comment>
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{D70BFC1C-14D4-49E7-B972-46D3754A3AA5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="BIZ UDPゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>【祭礼役員】 10時までに
+・</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color indexed="10"/>
+            <rFont val="BIZ UDPゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山車の移動（行政センター➡駒寄会館）</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="BIZ UDPゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+・神輿／山車の最終点検
+　（電飾：大野）</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F15" authorId="0" shapeId="0" xr:uid="{63A5E411-0CB8-4EE7-A16F-EDC487C4F401}">
       <text>
         <r>
@@ -171,6 +211,41 @@
         </r>
       </text>
     </comment>
+    <comment ref="C30" authorId="1" shapeId="0" xr:uid="{1412EF6F-90AB-4F50-8A41-F08D8444D974}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="BIZ UDPゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>【青壮年部】
+神社神輿　宮出しお手伝い（神社～）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F36" authorId="0" shapeId="0" xr:uid="{E83B52B1-624A-4C48-B377-5F6BD66CF2CB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="BIZ UDPゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">神輿長：伊藤大樹／（副）松村英治
+子供神輿長：杉山（少年部部長）
+山車長：
+警護：青山、松川、高橋、佐久間明
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="I36" authorId="0" shapeId="0" xr:uid="{CAB2AC08-EF1D-4148-BA17-6B2C726520F2}">
       <text>
         <r>
@@ -197,8 +272,8 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t>今年の担当は
-【駒寄】</t>
+          <t>Ｒ８年の担当は
+【駒寄】です</t>
         </r>
       </text>
     </comment>
@@ -217,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{3C30F78B-4D4E-4D1F-BBF0-F033C0441CD3}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{6B5E31D6-60CF-43C2-B08A-1C0E5F59B875}">
       <text>
         <r>
           <rPr>
@@ -234,7 +309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{CB7E515D-965B-48AF-AF14-0DDC5B7209AC}">
+    <comment ref="F52" authorId="0" shapeId="0" xr:uid="{504A3EFF-1746-406E-9478-8698E4146735}">
       <text>
         <r>
           <rPr>
@@ -251,56 +326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F50" authorId="0" shapeId="0" xr:uid="{89049B3B-9BE8-4F0B-AB27-F855210B4244}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color indexed="81"/>
-            <rFont val="BIZ UDPゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>御仮屋前を通過する際、各町内神輿は神社神輿にさす</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{ED365A1F-4CFA-4185-9502-EA6BBFF573A6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color indexed="81"/>
-            <rFont val="BIZ UDPゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>【祭礼役員】リヤカー
-・ジャグ（小）×１, 
-紙コップ、ゴミ袋</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{CD7E4F17-660D-498B-837C-5870131F26F3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color indexed="81"/>
-            <rFont val="BIZ UDPゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>【祭礼役員】リヤカー
-・ジャグ（小）×１, 
-紙コップ、ゴミ袋</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I59" authorId="0" shapeId="0" xr:uid="{E8AA172C-0FDC-4A8A-8A4A-AFF8491083CD}">
+    <comment ref="I56" authorId="0" shapeId="0" xr:uid="{E9A30FE2-BE71-49D1-9CCE-9DEC7AF1DD17}">
       <text>
         <r>
           <rPr>
@@ -312,9 +338,7 @@
             <charset val="128"/>
           </rPr>
           <t>【大野】山車の移動
-　※駒寄の神輿が
-　　　マンション前を通過
-　　　した後に収納を開始。</t>
+　</t>
         </r>
       </text>
     </comment>
@@ -373,6 +397,21 @@
             <charset val="128"/>
           </rPr>
           <t>神輿台持ち：駒寄⑦～⑨</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{DF317ADA-B287-453D-ADE8-53BFAC05CB31}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="12"/>
+            <color indexed="10"/>
+            <rFont val="BIZ UDPゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>11:40 集合　遅刻厳禁</t>
         </r>
       </text>
     </comment>
@@ -437,7 +476,8 @@
             <charset val="128"/>
           </rPr>
           <t>16:00～16:30
-　神社神輿　宮入
+【青壮年部】
+　神社神輿　宮入りのお手伝い
 　（ごはん亭～神社）　</t>
         </r>
       </text>
@@ -477,7 +517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="333">
   <si>
     <t>収入</t>
     <rPh sb="0" eb="2">
@@ -2222,17 +2262,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>⑩（各町内神輿は帰路へ）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>⑦ピザーラ着（19:40出発）</t>
-    <rPh sb="5" eb="6">
-      <t>チャク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>※駒寄帰着予定時刻：21:15</t>
     <rPh sb="1" eb="3">
       <t>コマヨセ</t>
@@ -2245,16 +2274,6 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>ジコク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>②セブンイレブン前通過➡</t>
-    <rPh sb="8" eb="9">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ツウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3031,13 +3050,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>休憩（20:15出発）</t>
-    <rPh sb="0" eb="2">
-      <t>キュウケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>①四町内 駒寄会館前集合</t>
     <rPh sb="1" eb="2">
       <t>ヨン</t>
@@ -3053,24 +3065,6 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>シュウゴウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>会館（出発）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>③船越タクシー前　着</t>
-    <rPh sb="9" eb="10">
-      <t>チャク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>⑨セブンイレブン前　着</t>
-    <rPh sb="10" eb="11">
-      <t>チャク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3764,6 +3758,149 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>山車の収納（行政センター）</t>
+    <rPh sb="6" eb="8">
+      <t>ギョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①会館（立ち上げ）</t>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セブンイレブン前通過➡</t>
+    <rPh sb="7" eb="8">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ツウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②船越タクシー前　着</t>
+    <rPh sb="9" eb="10">
+      <t>チャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>休憩（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="BIZ UDP明朝 Medium"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>19:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="BIZ UDP明朝 Medium"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>出発）</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>キュウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③ピザーラ前　着</t>
+    <rPh sb="5" eb="6">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>チャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④セブンイレブン前　着</t>
+    <rPh sb="10" eb="11">
+      <t>チャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>休憩（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="BIZ UDP明朝 Medium"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>20:15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="BIZ UDP明朝 Medium"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>出発）</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>キュウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤（各町内神輿は帰路へ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※21時までに？格納完了</t>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※太鼓（参加は自由）</t>
+    <rPh sb="1" eb="3">
+      <t>タイコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サンカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -3774,7 +3911,7 @@
     <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="#,##0;&quot;△ &quot;#,##0"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4087,6 +4224,22 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="10"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -4150,7 +4303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -4571,17 +4724,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4589,7 +4731,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="347">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4934,9 +5076,6 @@
     <xf numFmtId="0" fontId="24" fillId="9" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="25" fillId="9" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4964,9 +5103,6 @@
     <xf numFmtId="0" fontId="26" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5249,15 +5385,9 @@
     <xf numFmtId="0" fontId="22" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="20" fontId="25" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="24" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -5345,12 +5475,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="24" fillId="10" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="24" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -5426,9 +5550,6 @@
     <xf numFmtId="20" fontId="24" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -5456,15 +5577,9 @@
     <xf numFmtId="0" fontId="28" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -5572,6 +5687,48 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="28" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="24" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="9" borderId="26" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="24" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="24" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5786,8 +5943,8 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>134470</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>134676</xdr:rowOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>58615</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
@@ -5808,8 +5965,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1458445" y="10002576"/>
-          <a:ext cx="2064443" cy="3413106"/>
+          <a:off x="1453316" y="10345615"/>
+          <a:ext cx="2064443" cy="4054805"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5945,8 +6102,8 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>2155371</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>161364</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5961,8 +6118,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7760634" y="10232091"/>
-          <a:ext cx="2119512" cy="3192556"/>
+          <a:off x="7745506" y="11116235"/>
+          <a:ext cx="2119512" cy="2554941"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6095,8 +6252,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="678785" y="465484"/>
-          <a:ext cx="372872" cy="16064090"/>
+          <a:off x="682233" y="465484"/>
+          <a:ext cx="370458" cy="16130291"/>
           <a:chOff x="781879" y="465484"/>
           <a:chExt cx="367109" cy="15271994"/>
         </a:xfrm>
@@ -8164,1743 +8321,2173 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2534478</xdr:colOff>
+      <xdr:colOff>2546850</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>443713</xdr:rowOff>
+      <xdr:rowOff>398890</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>49530</xdr:colOff>
+      <xdr:colOff>19859</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>236221</xdr:rowOff>
+      <xdr:rowOff>191388</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="45" name="グループ化 44">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="四角形: 角を丸くする 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C69ECF-080B-4115-AA79-453A77C2F0B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDA1B50A-7DC0-DB62-3812-FEF0F5AB867B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="3852290" y="443713"/>
-          <a:ext cx="374793" cy="16063449"/>
-          <a:chOff x="781879" y="465484"/>
-          <a:chExt cx="367109" cy="15271994"/>
+          <a:off x="3865696" y="398890"/>
+          <a:ext cx="333440" cy="16128606"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="46" name="四角形: 角を丸くする 45">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDA1B50A-7DC0-DB62-3812-FEF0F5AB867B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="785193" y="465484"/>
-            <a:ext cx="326003" cy="15271994"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:gradFill flip="none" rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="67000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="48000">
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="97000"/>
-                  <a:lumOff val="3000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="1"/>
-            <a:tileRect/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="47" name="テキスト ボックス 46">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EB5C8B4-E7E7-8137-7D97-8CCEE5356ECC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="843169" y="540027"/>
-            <a:ext cx="262636" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill flip="none" rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="accent6">
+                <a:lumMod val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="48000">
+              <a:schemeClr val="accent6">
+                <a:lumMod val="97000"/>
+                <a:lumOff val="3000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
+        </a:gradFill>
+        <a:ln>
           <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-              <a:t>8</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="48" name="正方形/長方形 47">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{328DFF58-B180-6E7D-2B7F-ECFEF5A744B4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="834887" y="482048"/>
-            <a:ext cx="265043" cy="1485664"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>35675</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>65419</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>5363</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>109295</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="テキスト ボックス 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EB5C8B4-E7E7-8137-7D97-8CCEE5356ECC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3916013" y="522619"/>
+          <a:ext cx="268627" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>8</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>27204</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>4188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>298293</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>60906</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="正方形/長方形 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{328DFF58-B180-6E7D-2B7F-ECFEF5A744B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3907542" y="461388"/>
+          <a:ext cx="271089" cy="1568995"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="49" name="テキスト ボックス 48">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF66A940-4749-4D62-6F30-21A2A94A1332}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="829916" y="1971025"/>
-            <a:ext cx="262636" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-              <a:t>9</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="50" name="正方形/長方形 49">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2596270-A482-C300-EFA6-701D36B86E27}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="838200" y="1962743"/>
-            <a:ext cx="265043" cy="1463892"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22120</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>64406</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>290747</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108282</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="テキスト ボックス 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF66A940-4749-4D62-6F30-21A2A94A1332}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3902458" y="2033883"/>
+          <a:ext cx="268627" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>9</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>30593</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>55659</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2743</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>89384</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="正方形/長方形 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2596270-A482-C300-EFA6-701D36B86E27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3910931" y="2025136"/>
+          <a:ext cx="271089" cy="1546002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="51" name="テキスト ボックス 50">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6DA9F37-16BC-E5E2-10EE-7B6529114BCC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="808382" y="3493131"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-              <a:t>10</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="52" name="正方形/長方形 51">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00D6B664-7A29-5CC1-0464-E0BFAD2521CF}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="833230" y="3458109"/>
-            <a:ext cx="265043" cy="257327"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>95</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>159610</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>49532</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>203486</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="テキスト ボックス 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6DA9F37-16BC-E5E2-10EE-7B6529114BCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3880433" y="3641364"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>10</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>25509</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>122624</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>296598</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>142339</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="正方形/長方形 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00D6B664-7A29-5CC1-0464-E0BFAD2521CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3905847" y="3604378"/>
+          <a:ext cx="271089" cy="271761"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="53" name="テキスト ボックス 52">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE949A46-A4B1-CD7E-F588-156352456AE5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="803412" y="3746817"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-              <a:t>11</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="54" name="正方形/長方形 53">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C483580D-99B5-BB7A-6EFD-6552818EE4F9}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="836543" y="3728594"/>
-            <a:ext cx="265043" cy="237877"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2556503</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>175479</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>44448</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>219355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="テキスト ボックス 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE949A46-A4B1-CD7E-F588-156352456AE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3875349" y="3909279"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>11</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28898</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>156234</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1048</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>155408</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="正方形/長方形 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C483580D-99B5-BB7A-6EFD-6552818EE4F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3909236" y="3890034"/>
+          <a:ext cx="271089" cy="251220"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="55" name="テキスト ボックス 54">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FD1A417-4D12-0352-F9EC-534B2F3A5232}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="781879" y="3962497"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>12</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2534479</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>151211</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>22424</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>195087</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="テキスト ボックス 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FD1A417-4D12-0352-F9EC-534B2F3A5232}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3853325" y="4137057"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="56" name="正方形/長方形 55">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E85B06C-A416-5ECE-87F5-FE7BF4E8E1B4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="823292" y="3983935"/>
-            <a:ext cx="265043" cy="427618"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>12</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
               </a:schemeClr>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>15345</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>173852</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>286434</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>121363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="正方形/長方形 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E85B06C-A416-5ECE-87F5-FE7BF4E8E1B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3895683" y="4159698"/>
+          <a:ext cx="271089" cy="451603"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="57" name="テキスト ボックス 56">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19FBB8CD-4A6C-42E1-A511-C4016E74FB9D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="793473" y="4461249"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>13</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2546337</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>173846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>34282</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>217721</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="テキスト ボックス 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19FBB8CD-4A6C-42E1-A511-C4016E74FB9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3865183" y="4663784"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="58" name="正方形/長方形 57">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E6200C1-EA31-9BF6-15F1-5B12F12B7E21}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="834887" y="4444686"/>
-            <a:ext cx="265043" cy="310242"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>13</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
               </a:schemeClr>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>27204</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>156354</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>298293</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>231951</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="正方形/長方形 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E6200C1-EA31-9BF6-15F1-5B12F12B7E21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3907542" y="4646292"/>
+          <a:ext cx="271089" cy="327644"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="59" name="テキスト ボックス 58">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D1A8A7C-9557-BDEC-2578-7B565FF87FA6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="788504" y="4816218"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>14</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2541255</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44633</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>29200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>88509</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="テキスト ボックス 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D1A8A7C-9557-BDEC-2578-7B565FF87FA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3860101" y="5038664"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="60" name="正方形/長方形 59">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23F7039D-3820-D428-9DB4-8E558BD618F5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="829918" y="4807936"/>
-            <a:ext cx="265043" cy="896887"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>14</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
               </a:schemeClr>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22122</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>35886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>293211</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>226942</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="正方形/長方形 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23F7039D-3820-D428-9DB4-8E558BD618F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3902460" y="5029917"/>
+          <a:ext cx="271089" cy="947194"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="61" name="テキスト ボックス 60">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D759C30-23F0-0236-C5E4-8A65FEF0BE23}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="801756" y="5704825"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>15</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2554809</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>226944</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>42754</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>18773</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="テキスト ボックス 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D759C30-23F0-0236-C5E4-8A65FEF0BE23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3873655" y="5977113"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="62" name="正方形/長方形 61">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94A67D36-65EB-0832-CC4F-90235C2955BA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="824948" y="5721627"/>
-            <a:ext cx="265043" cy="968117"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>15</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
               </a:schemeClr>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>17038</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>244688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>288127</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>6876</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="正方形/長方形 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94A67D36-65EB-0832-CC4F-90235C2955BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3897376" y="5994857"/>
+          <a:ext cx="271089" cy="1022419"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="63" name="テキスト ボックス 62">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D45D7E-3BF5-4700-2398-B3421C7DA90D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="796786" y="6709623"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>16</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2549726</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>27870</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>37671</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>71746</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="テキスト ボックス 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D45D7E-3BF5-4700-2398-B3421C7DA90D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3868572" y="7038270"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="64" name="正方形/長方形 63">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B890458-55B0-FC84-44CF-50F752AE968B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="828261" y="6726426"/>
-            <a:ext cx="265043" cy="1473830"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>16</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
               </a:schemeClr>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>20427</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>45616</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>291516</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>89837</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="正方形/長方形 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B890458-55B0-FC84-44CF-50F752AE968B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3900765" y="7056016"/>
+          <a:ext cx="271089" cy="1556498"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="65" name="テキスト ボックス 64">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45A09ACC-DA43-CF27-46DC-2B77E84A4133}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="791816" y="8206883"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>17</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2544643</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>96835</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>32588</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>140711</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="テキスト ボックス 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45A09ACC-DA43-CF27-46DC-2B77E84A4133}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3863489" y="8619512"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="66" name="正方形/長方形 65">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1877859B-F8D5-1F8A-704F-ED7BA52E40F8}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="823292" y="8231967"/>
-            <a:ext cx="265043" cy="1246886"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>17</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>15345</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123326</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>286434</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>179919</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="正方形/長方形 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1877859B-F8D5-1F8A-704F-ED7BA52E40F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3895683" y="8646003"/>
+          <a:ext cx="271089" cy="1316824"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="67" name="テキスト ボックス 66">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A24B9C56-8719-F96F-444D-AC17B0B39483}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="803412" y="9472228"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>18</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2556503</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>172923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>44448</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>216799</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="67" name="テキスト ボックス 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A24B9C56-8719-F96F-444D-AC17B0B39483}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3875349" y="9955831"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="68" name="正方形/長方形 67">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{212D0550-B02B-88F9-9A0B-A6EF6C409758}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="826605" y="9487137"/>
-            <a:ext cx="265043" cy="1709294"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>18</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>18733</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>188669</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>289822</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>5862</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="68" name="正方形/長方形 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{212D0550-B02B-88F9-9A0B-A6EF6C409758}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3899071" y="9971577"/>
+          <a:ext cx="271089" cy="1329470"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="69" name="テキスト ボックス 68">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA19C6BC-3CF2-7D0A-5A89-1F9506896FD9}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="798442" y="11244706"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>19</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2557282</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>5005</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>45227</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>48881</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="69" name="テキスト ボックス 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA19C6BC-3CF2-7D0A-5A89-1F9506896FD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3876128" y="11300190"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="70" name="正方形/長方形 69">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{274DF305-2C8C-59F9-A097-8719B833728B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="829918" y="11226485"/>
-            <a:ext cx="265043" cy="1213520"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>19</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22122</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>35169</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>293211</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>246184</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="70" name="正方形/長方形 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{274DF305-2C8C-59F9-A097-8719B833728B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3902460" y="11330354"/>
+          <a:ext cx="271089" cy="1471245"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="71" name="テキスト ボックス 70">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52A9B579-B814-5E68-A010-49375B3E80BC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="793472" y="12456571"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>20</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2546336</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>1167</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>34281</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>45043</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="71" name="テキスト ボックス 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52A9B579-B814-5E68-A010-49375B3E80BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3865182" y="12808629"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="72" name="正方形/長方形 71">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EDC38E8-04FB-5CDC-1E0C-B533C10CCCD1}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="824947" y="12471480"/>
-            <a:ext cx="265043" cy="1203817"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>20</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>17037</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>29307</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>288126</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>74914</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="正方形/長方形 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EDC38E8-04FB-5CDC-1E0C-B533C10CCCD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3897375" y="12836769"/>
+          <a:ext cx="271089" cy="1557883"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="50000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="73" name="テキスト ボックス 72">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B12D8478-5E3F-E5D1-DC49-1424535548FC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="796785" y="13738483"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>21</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2549725</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>141644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>37670</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>185519</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="73" name="テキスト ボックス 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B12D8478-5E3F-E5D1-DC49-1424535548FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3868571" y="14461382"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="74" name="正方形/長方形 73">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF3C0EC-8DDA-0E5F-86C5-4B4375C7640E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="819977" y="13728546"/>
-            <a:ext cx="265043" cy="472342"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>21</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>11954</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>131149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>283043</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>125892</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="74" name="正方形/長方形 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF3C0EC-8DDA-0E5F-86C5-4B4375C7640E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3892292" y="14450887"/>
+          <a:ext cx="271089" cy="498836"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="50000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="75" name="テキスト ボックス 74">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE4FAD4-0C98-0E5E-6233-2558BF817EAC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="791816" y="14224080"/>
-            <a:ext cx="340606" cy="280205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>22</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2544643</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>150385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>32588</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>194261</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="75" name="テキスト ボックス 74">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE4FAD4-0C98-0E5E-6233-2558BF817EAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3863489" y="14974216"/>
+          <a:ext cx="348376" cy="295922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="76" name="正方形/長方形 75">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51AD111D-EC4E-6612-D057-C9699A3B31DC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="815007" y="14249165"/>
-            <a:ext cx="295336" cy="1448035"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
+            </a:rPr>
+            <a:t>22</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6871</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>176877</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>10005</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>193856</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="76" name="正方形/長方形 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51AD111D-EC4E-6612-D057-C9699A3B31DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3887209" y="15000708"/>
+          <a:ext cx="302073" cy="1529256"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="50000"/>
             </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -9929,8 +10516,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7093032" y="448837"/>
-          <a:ext cx="350460" cy="16063449"/>
+          <a:off x="7094756" y="448837"/>
+          <a:ext cx="352874" cy="16128616"/>
           <a:chOff x="781879" y="465484"/>
           <a:chExt cx="367109" cy="15271994"/>
         </a:xfrm>
@@ -11671,8 +12258,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10094288" y="465485"/>
-          <a:ext cx="368389" cy="16064090"/>
+          <a:off x="10102563" y="465485"/>
+          <a:ext cx="370458" cy="16130291"/>
           <a:chOff x="781879" y="465484"/>
           <a:chExt cx="367109" cy="15271994"/>
         </a:xfrm>
@@ -13435,6 +14022,74 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28898</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>156234</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1048</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>155408</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="143" name="正方形/長方形 142">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{611569DD-1AB6-4C4F-80E9-0CEAD138B80B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3909236" y="3890034"/>
+          <a:ext cx="271089" cy="251220"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -22104,43 +22759,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:10" ht="36" customHeight="1">
-      <c r="C1" s="340" t="s">
+      <c r="C1" s="331" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="340"/>
+      <c r="D1" s="331"/>
       <c r="E1" s="84"/>
-      <c r="F1" s="340" t="s">
+      <c r="F1" s="331" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="340"/>
-      <c r="I1" s="340" t="s">
+      <c r="G1" s="331"/>
+      <c r="I1" s="331" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="340"/>
+      <c r="J1" s="331"/>
     </row>
     <row r="2" spans="3:10" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="C2" s="341"/>
-      <c r="D2" s="341"/>
+      <c r="C2" s="332"/>
+      <c r="D2" s="332"/>
       <c r="E2" s="86"/>
       <c r="F2" s="89" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G2" s="87" t="s">
         <v>111</v>
       </c>
       <c r="H2" s="86"/>
-      <c r="I2" s="341"/>
-      <c r="J2" s="341"/>
+      <c r="I2" s="332"/>
+      <c r="J2" s="332"/>
     </row>
     <row r="3" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C3" s="87"/>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
       <c r="F3" s="89" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G3" s="87" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H3" s="101"/>
       <c r="I3" s="89"/>
@@ -22164,23 +22819,23 @@
       <c r="E5" s="86"/>
       <c r="F5" s="91"/>
       <c r="G5" s="90" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H5" s="86"/>
       <c r="I5" s="87"/>
       <c r="J5" s="86"/>
     </row>
     <row r="6" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C6" s="268" t="s">
-        <v>240</v>
+      <c r="C6" s="264" t="s">
+        <v>237</v>
       </c>
       <c r="D6" s="86" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E6" s="86"/>
       <c r="F6" s="91"/>
-      <c r="G6" s="148" t="s">
-        <v>228</v>
+      <c r="G6" s="146" t="s">
+        <v>225</v>
       </c>
       <c r="H6" s="86"/>
       <c r="I6" s="87"/>
@@ -22188,33 +22843,33 @@
     </row>
     <row r="7" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C7" s="92"/>
-      <c r="D7" s="311" t="s">
-        <v>259</v>
+      <c r="D7" s="302" t="s">
+        <v>256</v>
       </c>
       <c r="E7" s="93"/>
       <c r="F7" s="92"/>
       <c r="G7" s="94"/>
       <c r="H7" s="86"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="212"/>
+      <c r="I7" s="209"/>
+      <c r="J7" s="210"/>
     </row>
     <row r="8" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C8" s="95" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E8" s="88"/>
       <c r="F8" s="89" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G8" s="97" t="s">
         <v>181</v>
       </c>
-      <c r="H8" s="210"/>
-      <c r="I8" s="213"/>
-      <c r="J8" s="214"/>
+      <c r="H8" s="208"/>
+      <c r="I8" s="211"/>
+      <c r="J8" s="212"/>
     </row>
     <row r="9" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C9" s="99"/>
@@ -22222,7 +22877,7 @@
       <c r="E9" s="86"/>
       <c r="F9" s="87"/>
       <c r="G9" s="90" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H9" s="101"/>
       <c r="I9" s="87"/>
@@ -22262,31 +22917,31 @@
       <c r="C13" s="99"/>
       <c r="D13" s="100"/>
       <c r="E13" s="86"/>
-      <c r="F13" s="211"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="212"/>
-      <c r="I13" s="211"/>
-      <c r="J13" s="212"/>
+      <c r="F13" s="209"/>
+      <c r="G13" s="210"/>
+      <c r="H13" s="210"/>
+      <c r="I13" s="209"/>
+      <c r="J13" s="210"/>
     </row>
     <row r="14" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C14" s="276"/>
-      <c r="D14" s="277"/>
+      <c r="C14" s="270"/>
+      <c r="D14" s="271"/>
       <c r="E14" s="86"/>
-      <c r="F14" s="211"/>
-      <c r="G14" s="212"/>
-      <c r="H14" s="215"/>
-      <c r="I14" s="211"/>
-      <c r="J14" s="212"/>
+      <c r="F14" s="219"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="213"/>
+      <c r="I14" s="209"/>
+      <c r="J14" s="210"/>
     </row>
     <row r="15" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C15" s="202"/>
+      <c r="C15" s="200"/>
       <c r="D15" s="102"/>
       <c r="E15" s="86"/>
-      <c r="F15" s="221"/>
-      <c r="G15" s="212"/>
-      <c r="H15" s="212"/>
-      <c r="I15" s="274"/>
-      <c r="J15" s="275"/>
+      <c r="F15" s="219"/>
+      <c r="G15" s="210"/>
+      <c r="H15" s="210"/>
+      <c r="I15" s="268"/>
+      <c r="J15" s="269"/>
     </row>
     <row r="16" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C16" s="103"/>
@@ -22311,18 +22966,18 @@
       <c r="J17" s="86"/>
     </row>
     <row r="18" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C18" s="278" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" s="279" t="s">
-        <v>260</v>
-      </c>
-      <c r="E18" s="275"/>
-      <c r="F18" s="280"/>
-      <c r="G18" s="281"/>
-      <c r="H18" s="275"/>
-      <c r="I18" s="274"/>
-      <c r="J18" s="275"/>
+      <c r="C18" s="272" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" s="273" t="s">
+        <v>257</v>
+      </c>
+      <c r="E18" s="269"/>
+      <c r="F18" s="274"/>
+      <c r="G18" s="275"/>
+      <c r="H18" s="269"/>
+      <c r="I18" s="268"/>
+      <c r="J18" s="269"/>
     </row>
     <row r="19" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C19" s="99"/>
@@ -22331,65 +22986,65 @@
       <c r="F19" s="89"/>
       <c r="G19" s="105"/>
       <c r="H19" s="105"/>
-      <c r="I19" s="282"/>
-      <c r="J19" s="283"/>
+      <c r="I19" s="276"/>
+      <c r="J19" s="277"/>
     </row>
     <row r="20" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C20" s="99"/>
-      <c r="D20" s="306" t="s">
-        <v>250</v>
+      <c r="D20" s="299" t="s">
+        <v>247</v>
       </c>
       <c r="E20" s="86"/>
       <c r="F20" s="89"/>
       <c r="G20" s="105"/>
       <c r="H20" s="106"/>
-      <c r="I20" s="284"/>
+      <c r="I20" s="278"/>
       <c r="J20" s="106"/>
     </row>
     <row r="21" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C21" s="107"/>
       <c r="D21" s="108" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E21" s="86"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="204" t="s">
-        <v>326</v>
+      <c r="F21" s="201"/>
+      <c r="G21" s="202" t="s">
+        <v>319</v>
       </c>
       <c r="H21" s="90"/>
       <c r="I21" s="89"/>
       <c r="J21" s="90"/>
     </row>
     <row r="22" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C22" s="224" t="s">
-        <v>193</v>
-      </c>
-      <c r="D22" s="225" t="s">
-        <v>242</v>
-      </c>
-      <c r="E22" s="212"/>
-      <c r="F22" s="224" t="s">
-        <v>193</v>
-      </c>
-      <c r="G22" s="226" t="s">
+      <c r="C22" s="222" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" s="223" t="s">
+        <v>239</v>
+      </c>
+      <c r="E22" s="210"/>
+      <c r="F22" s="222" t="s">
+        <v>190</v>
+      </c>
+      <c r="G22" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="H22" s="216"/>
-      <c r="I22" s="216"/>
-      <c r="J22" s="216"/>
+      <c r="H22" s="214"/>
+      <c r="I22" s="214"/>
+      <c r="J22" s="214"/>
     </row>
     <row r="23" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C23" s="114" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D23" s="110" t="s">
         <v>174</v>
       </c>
       <c r="E23" s="101"/>
       <c r="F23" s="109" t="s">
-        <v>191</v>
-      </c>
-      <c r="G23" s="205" t="s">
+        <v>188</v>
+      </c>
+      <c r="G23" s="203" t="s">
         <v>177</v>
       </c>
       <c r="H23" s="111"/>
@@ -22401,15 +23056,15 @@
       <c r="D24" s="110"/>
       <c r="E24" s="86"/>
       <c r="F24" s="109" t="s">
-        <v>198</v>
-      </c>
-      <c r="G24" s="205" t="s">
+        <v>195</v>
+      </c>
+      <c r="G24" s="203" t="s">
         <v>178</v>
       </c>
       <c r="H24" s="113"/>
-      <c r="I24" s="217"/>
-      <c r="J24" s="299" t="s">
-        <v>243</v>
+      <c r="I24" s="215"/>
+      <c r="J24" s="292" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -22417,98 +23072,98 @@
       <c r="D25" s="110"/>
       <c r="E25" s="111"/>
       <c r="F25" s="109" t="s">
-        <v>192</v>
-      </c>
-      <c r="G25" s="205" t="s">
+        <v>189</v>
+      </c>
+      <c r="G25" s="203" t="s">
         <v>179</v>
       </c>
       <c r="H25" s="90"/>
       <c r="I25" s="109" t="s">
-        <v>192</v>
-      </c>
-      <c r="J25" s="205" t="s">
-        <v>244</v>
+        <v>189</v>
+      </c>
+      <c r="J25" s="203" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="3:10" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="C26" s="335"/>
-      <c r="D26" s="336"/>
+      <c r="C26" s="326"/>
+      <c r="D26" s="327"/>
       <c r="E26" s="110"/>
-      <c r="F26" s="224" t="s">
-        <v>193</v>
-      </c>
-      <c r="G26" s="330" t="s">
-        <v>245</v>
-      </c>
-      <c r="H26" s="216"/>
-      <c r="I26" s="228"/>
-      <c r="J26" s="228" t="s">
-        <v>231</v>
+      <c r="F26" s="222" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="321" t="s">
+        <v>242</v>
+      </c>
+      <c r="H26" s="214"/>
+      <c r="I26" s="226"/>
+      <c r="J26" s="226" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C27" s="338" t="s">
-        <v>191</v>
+      <c r="C27" s="329" t="s">
+        <v>188</v>
       </c>
       <c r="D27" s="110" t="s">
         <v>175</v>
       </c>
       <c r="E27" s="86"/>
       <c r="F27" s="109" t="s">
-        <v>191</v>
-      </c>
-      <c r="G27" s="331" t="s">
-        <v>220</v>
+        <v>188</v>
+      </c>
+      <c r="G27" s="322" t="s">
+        <v>217</v>
       </c>
       <c r="H27" s="86"/>
-      <c r="I27" s="227"/>
+      <c r="I27" s="225"/>
       <c r="J27" s="125" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="3:10" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="C28" s="112"/>
       <c r="D28" s="110"/>
       <c r="E28" s="86"/>
-      <c r="F28" s="206"/>
-      <c r="G28" s="332" t="s">
-        <v>251</v>
+      <c r="F28" s="204"/>
+      <c r="G28" s="323" t="s">
+        <v>248</v>
       </c>
       <c r="H28" s="86"/>
-      <c r="I28" s="209"/>
+      <c r="I28" s="207"/>
       <c r="J28" s="115" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C29" s="117"/>
       <c r="D29" s="118"/>
       <c r="E29" s="86"/>
-      <c r="F29" s="207" t="s">
-        <v>198</v>
-      </c>
-      <c r="G29" s="208" t="s">
+      <c r="F29" s="205" t="s">
+        <v>195</v>
+      </c>
+      <c r="G29" s="206" t="s">
         <v>180</v>
       </c>
       <c r="H29" s="86"/>
       <c r="I29" s="116" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J29" s="119" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C30" s="117" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D30" s="120" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E30" s="86"/>
       <c r="F30" s="89"/>
-      <c r="G30" s="161" t="s">
-        <v>247</v>
+      <c r="G30" s="159" t="s">
+        <v>244</v>
       </c>
       <c r="H30" s="105"/>
       <c r="I30" s="116"/>
@@ -22518,29 +23173,29 @@
     </row>
     <row r="31" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C31" s="109" t="s">
-        <v>193</v>
-      </c>
-      <c r="D31" s="228" t="s">
-        <v>291</v>
+        <v>190</v>
+      </c>
+      <c r="D31" s="226" t="s">
+        <v>284</v>
       </c>
       <c r="E31" s="86"/>
       <c r="F31" s="89"/>
-      <c r="G31" s="161"/>
+      <c r="G31" s="159"/>
       <c r="H31" s="105"/>
       <c r="I31" s="116"/>
       <c r="J31" s="119"/>
     </row>
     <row r="32" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C32" s="224" t="s">
-        <v>194</v>
-      </c>
-      <c r="D32" s="228" t="s">
-        <v>289</v>
+      <c r="C32" s="222" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="226" t="s">
+        <v>282</v>
       </c>
       <c r="E32" s="90"/>
       <c r="F32" s="89"/>
-      <c r="G32" s="251" t="s">
-        <v>246</v>
+      <c r="G32" s="247" t="s">
+        <v>243</v>
       </c>
       <c r="H32" s="105"/>
       <c r="I32" s="116"/>
@@ -22549,62 +23204,62 @@
       </c>
     </row>
     <row r="33" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C33" s="224" t="s">
-        <v>223</v>
+      <c r="C33" s="222" t="s">
+        <v>220</v>
       </c>
       <c r="D33" s="120" t="s">
-        <v>292</v>
-      </c>
-      <c r="E33" s="212"/>
-      <c r="F33" s="222"/>
-      <c r="G33" s="223"/>
-      <c r="H33" s="223"/>
-      <c r="I33" s="230"/>
-      <c r="J33" s="231" t="s">
-        <v>253</v>
+        <v>285</v>
+      </c>
+      <c r="E33" s="210"/>
+      <c r="F33" s="220"/>
+      <c r="G33" s="221"/>
+      <c r="H33" s="221"/>
+      <c r="I33" s="228"/>
+      <c r="J33" s="229" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C34" s="109" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D34" s="120" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E34" s="86"/>
       <c r="F34" s="89"/>
       <c r="G34" s="105"/>
       <c r="H34" s="105"/>
-      <c r="I34" s="229"/>
+      <c r="I34" s="227"/>
       <c r="J34" s="119" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C35" s="334"/>
+      <c r="C35" s="325"/>
       <c r="D35" s="120" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E35" s="86"/>
       <c r="F35" s="89"/>
       <c r="G35" s="105"/>
       <c r="H35" s="105"/>
-      <c r="I35" s="220" t="s">
-        <v>198</v>
+      <c r="I35" s="218" t="s">
+        <v>195</v>
       </c>
       <c r="J35" s="121" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C36" s="109" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D36" s="120" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="E36" s="86"/>
-      <c r="F36" s="89"/>
+      <c r="F36" s="122"/>
       <c r="G36" s="105"/>
       <c r="H36" s="105"/>
       <c r="I36" s="122"/>
@@ -22612,10 +23267,10 @@
     </row>
     <row r="37" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C37" s="109" t="s">
-        <v>202</v>
-      </c>
-      <c r="D37" s="228" t="s">
-        <v>295</v>
+        <v>199</v>
+      </c>
+      <c r="D37" s="226" t="s">
+        <v>288</v>
       </c>
       <c r="E37" s="86"/>
       <c r="F37" s="89"/>
@@ -22625,11 +23280,11 @@
       <c r="J37" s="86"/>
     </row>
     <row r="38" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C38" s="224" t="s">
-        <v>192</v>
+      <c r="C38" s="222" t="s">
+        <v>189</v>
       </c>
       <c r="D38" s="120" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E38" s="86"/>
       <c r="F38" s="89"/>
@@ -22639,9 +23294,9 @@
       <c r="J38" s="86"/>
     </row>
     <row r="39" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C39" s="207"/>
-      <c r="D39" s="333" t="s">
-        <v>281</v>
+      <c r="C39" s="205"/>
+      <c r="D39" s="324" t="s">
+        <v>274</v>
       </c>
       <c r="E39" s="86"/>
       <c r="F39" s="89"/>
@@ -22656,7 +23311,7 @@
       <c r="E40" s="86"/>
       <c r="F40" s="123"/>
       <c r="G40" s="126" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H40" s="86"/>
       <c r="I40" s="87"/>
@@ -22666,32 +23321,28 @@
       <c r="C41" s="129"/>
       <c r="D41" s="90"/>
       <c r="E41" s="86"/>
-      <c r="F41" s="298" t="s">
-        <v>191</v>
-      </c>
-      <c r="G41" s="233" t="s">
+      <c r="F41" s="344" t="s">
+        <v>189</v>
+      </c>
+      <c r="G41" s="231" t="s">
         <v>182</v>
       </c>
       <c r="H41" s="86"/>
       <c r="I41" s="123"/>
       <c r="J41" s="124" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C42" s="129"/>
       <c r="D42" s="90"/>
       <c r="E42" s="86"/>
-      <c r="F42" s="132" t="s">
-        <v>198</v>
-      </c>
-      <c r="G42" s="133" t="s">
-        <v>270</v>
-      </c>
+      <c r="F42" s="136"/>
+      <c r="G42" s="133"/>
       <c r="H42" s="88"/>
       <c r="I42" s="127"/>
-      <c r="J42" s="294" t="s">
-        <v>239</v>
+      <c r="J42" s="349" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="43" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -22699,14 +23350,14 @@
       <c r="D43" s="90"/>
       <c r="E43" s="86"/>
       <c r="F43" s="132" t="s">
-        <v>193</v>
-      </c>
-      <c r="G43" s="314" t="s">
-        <v>271</v>
+        <v>190</v>
+      </c>
+      <c r="G43" s="133" t="s">
+        <v>266</v>
       </c>
       <c r="H43" s="105"/>
       <c r="I43" s="127" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J43" s="128" t="s">
         <v>117</v>
@@ -22716,75 +23367,65 @@
       <c r="C44" s="129"/>
       <c r="D44" s="90"/>
       <c r="E44" s="86"/>
-      <c r="F44" s="137"/>
-      <c r="G44" s="133" t="s">
-        <v>186</v>
-      </c>
       <c r="H44" s="111"/>
-      <c r="I44" s="135"/>
+      <c r="I44" s="134"/>
       <c r="J44" s="128"/>
     </row>
     <row r="45" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C45" s="129"/>
       <c r="D45" s="90"/>
       <c r="E45" s="86"/>
-      <c r="F45" s="137" t="s">
-        <v>197</v>
-      </c>
-      <c r="G45" s="138" t="s">
-        <v>272</v>
-      </c>
       <c r="H45" s="105"/>
       <c r="I45" s="128"/>
-      <c r="J45" s="136"/>
+      <c r="J45" s="135"/>
     </row>
     <row r="46" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C46" s="89"/>
       <c r="D46" s="86"/>
       <c r="E46" s="86"/>
-      <c r="F46" s="219"/>
-      <c r="G46" s="315" t="s">
-        <v>269</v>
+      <c r="F46" s="136" t="s">
+        <v>195</v>
+      </c>
+      <c r="G46" s="133" t="s">
+        <v>322</v>
       </c>
       <c r="H46" s="111"/>
       <c r="I46" s="128"/>
       <c r="J46" s="131"/>
     </row>
     <row r="47" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C47" s="211"/>
-      <c r="D47" s="212"/>
-      <c r="E47" s="212"/>
-      <c r="F47" s="232" t="s">
-        <v>201</v>
-      </c>
-      <c r="G47" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="H47" s="212"/>
-      <c r="I47" s="234"/>
-      <c r="J47" s="235"/>
+      <c r="C47" s="209"/>
+      <c r="D47" s="210"/>
+      <c r="E47" s="210"/>
+      <c r="F47" s="217"/>
+      <c r="G47" s="305" t="s">
+        <v>323</v>
+      </c>
+      <c r="H47" s="210"/>
+      <c r="I47" s="232"/>
+      <c r="J47" s="233"/>
     </row>
     <row r="48" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C48" s="87"/>
       <c r="D48" s="86"/>
       <c r="E48" s="86"/>
-      <c r="F48" s="137" t="s">
-        <v>198</v>
-      </c>
-      <c r="G48" s="138" t="s">
-        <v>184</v>
+      <c r="F48" s="345" t="s">
+        <v>189</v>
+      </c>
+      <c r="G48" s="137" t="s">
+        <v>324</v>
       </c>
       <c r="H48" s="90"/>
-      <c r="I48" s="139"/>
-      <c r="J48" s="139"/>
+      <c r="I48" s="138"/>
+      <c r="J48" s="138"/>
     </row>
     <row r="49" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C49" s="87"/>
       <c r="D49" s="86"/>
       <c r="E49" s="86"/>
-      <c r="F49" s="134"/>
-      <c r="G49" s="315" t="s">
-        <v>269</v>
+      <c r="F49" s="230"/>
+      <c r="G49" s="306" t="s">
+        <v>325</v>
       </c>
       <c r="H49" s="86"/>
       <c r="I49" s="130"/>
@@ -22794,9 +23435,9 @@
       <c r="C50" s="87"/>
       <c r="D50" s="86"/>
       <c r="E50" s="86"/>
-      <c r="F50" s="137"/>
-      <c r="G50" s="143" t="s">
-        <v>273</v>
+      <c r="F50" s="136"/>
+      <c r="G50" s="305" t="s">
+        <v>323</v>
       </c>
       <c r="H50" s="86"/>
       <c r="I50" s="130"/>
@@ -22806,118 +23447,128 @@
       <c r="C51" s="87"/>
       <c r="D51" s="86"/>
       <c r="E51" s="86"/>
-      <c r="F51" s="137"/>
-      <c r="G51" s="138"/>
+      <c r="F51" s="344" t="s">
+        <v>326</v>
+      </c>
+      <c r="G51" s="137" t="s">
+        <v>327</v>
+      </c>
       <c r="H51" s="90"/>
-      <c r="I51" s="139"/>
-      <c r="J51" s="139"/>
+      <c r="I51" s="138"/>
+      <c r="J51" s="138"/>
     </row>
     <row r="52" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C52" s="211"/>
-      <c r="D52" s="212"/>
-      <c r="E52" s="212"/>
-      <c r="F52" s="234"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="236"/>
-      <c r="I52" s="237"/>
-      <c r="J52" s="238"/>
+      <c r="C52" s="209"/>
+      <c r="D52" s="210"/>
+      <c r="E52" s="210"/>
+      <c r="F52" s="230"/>
+      <c r="G52" s="306" t="s">
+        <v>329</v>
+      </c>
+      <c r="H52" s="234"/>
+      <c r="I52" s="235"/>
+      <c r="J52" s="236"/>
     </row>
     <row r="53" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C53" s="87"/>
       <c r="D53" s="86"/>
       <c r="E53" s="86"/>
-      <c r="F53" s="137"/>
-      <c r="G53" s="138"/>
+      <c r="F53" s="345" t="s">
+        <v>199</v>
+      </c>
+      <c r="G53" s="142" t="s">
+        <v>328</v>
+      </c>
       <c r="H53" s="90"/>
-      <c r="I53" s="139"/>
-      <c r="J53" s="139"/>
+      <c r="I53" s="138"/>
+      <c r="J53" s="138"/>
     </row>
     <row r="54" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C54" s="87"/>
       <c r="D54" s="86"/>
       <c r="E54" s="86"/>
-      <c r="F54" s="132"/>
-      <c r="G54" s="143"/>
+      <c r="F54" s="300"/>
+      <c r="G54" s="346" t="s">
+        <v>267</v>
+      </c>
       <c r="H54" s="106"/>
-      <c r="I54" s="141"/>
-      <c r="J54" s="142"/>
+      <c r="I54" s="140"/>
+      <c r="J54" s="141"/>
     </row>
     <row r="55" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C55" s="87"/>
       <c r="D55" s="86"/>
       <c r="E55" s="86"/>
-      <c r="F55" s="307"/>
-      <c r="G55" s="308" t="s">
-        <v>274</v>
+      <c r="F55" s="344" t="s">
+        <v>190</v>
+      </c>
+      <c r="G55" s="142" t="s">
+        <v>330</v>
       </c>
       <c r="H55" s="90"/>
-      <c r="I55" s="139"/>
-      <c r="J55" s="139"/>
+      <c r="I55" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="J55" s="138" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="56" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C56" s="87"/>
       <c r="D56" s="86"/>
       <c r="E56" s="86"/>
-      <c r="F56" s="132" t="s">
-        <v>193</v>
-      </c>
-      <c r="G56" s="143" t="s">
+      <c r="H56" s="101"/>
+      <c r="I56" s="341"/>
+      <c r="J56" s="340" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C57" s="209"/>
+      <c r="D57" s="210"/>
+      <c r="E57" s="105"/>
+      <c r="F57" s="143"/>
+      <c r="G57" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="H56" s="101"/>
-      <c r="I56" s="130"/>
-      <c r="J56" s="144"/>
-    </row>
-    <row r="57" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C57" s="211"/>
-      <c r="D57" s="212"/>
-      <c r="E57" s="105"/>
-      <c r="F57" s="145"/>
-      <c r="G57" s="140" t="s">
-        <v>185</v>
-      </c>
       <c r="H57" s="86"/>
-      <c r="I57" s="234"/>
-      <c r="J57" s="235"/>
+      <c r="I57" s="232"/>
+      <c r="J57" s="233"/>
     </row>
     <row r="58" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C58" s="87"/>
       <c r="D58" s="86"/>
       <c r="E58" s="86"/>
-      <c r="F58" s="146"/>
-      <c r="G58" s="147" t="s">
-        <v>230</v>
+      <c r="F58" s="144"/>
+      <c r="G58" s="145" t="s">
+        <v>227</v>
       </c>
       <c r="H58" s="86"/>
-      <c r="I58" s="127" t="s">
-        <v>191</v>
-      </c>
-      <c r="J58" s="139" t="s">
-        <v>110</v>
-      </c>
+      <c r="I58" s="342"/>
+      <c r="J58" s="343"/>
     </row>
     <row r="59" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C59" s="211"/>
-      <c r="D59" s="212"/>
-      <c r="E59" s="212"/>
-      <c r="F59" s="310" t="s">
-        <v>198</v>
-      </c>
-      <c r="G59" s="297" t="s">
+      <c r="C59" s="209"/>
+      <c r="D59" s="210"/>
+      <c r="E59" s="210"/>
+      <c r="F59" s="347" t="s">
+        <v>195</v>
+      </c>
+      <c r="G59" s="291" t="s">
         <v>173</v>
       </c>
-      <c r="H59" s="212"/>
-      <c r="I59" s="241"/>
-      <c r="J59" s="212"/>
+      <c r="H59" s="210"/>
+      <c r="I59" s="87"/>
+      <c r="J59" s="210"/>
     </row>
     <row r="60" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C60" s="87"/>
       <c r="D60" s="86"/>
       <c r="E60" s="86"/>
-      <c r="F60" s="239" t="s">
-        <v>191</v>
-      </c>
-      <c r="G60" s="240" t="s">
+      <c r="F60" s="348" t="s">
+        <v>188</v>
+      </c>
+      <c r="G60" s="237" t="s">
         <v>103</v>
       </c>
       <c r="H60" s="86"/>
@@ -23017,916 +23668,916 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:14" ht="33.6" customHeight="1">
-      <c r="C1" s="340" t="s">
+      <c r="C1" s="331" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="340"/>
-      <c r="F1" s="340" t="s">
+      <c r="D1" s="331"/>
+      <c r="F1" s="331" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="340"/>
-      <c r="I1" s="340" t="s">
+      <c r="G1" s="331"/>
+      <c r="I1" s="331" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="340"/>
+      <c r="J1" s="331"/>
     </row>
     <row r="2" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C2" s="149"/>
+      <c r="C2" s="147"/>
       <c r="D2" s="86"/>
       <c r="E2" s="86"/>
-      <c r="F2" s="149"/>
+      <c r="F2" s="147"/>
       <c r="G2" s="86"/>
       <c r="H2" s="86"/>
-      <c r="I2" s="149"/>
+      <c r="I2" s="147"/>
       <c r="J2" s="86"/>
     </row>
     <row r="3" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C3" s="149"/>
+      <c r="C3" s="147"/>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
       <c r="H3" s="86"/>
-      <c r="I3" s="149"/>
+      <c r="I3" s="147"/>
       <c r="J3" s="86"/>
     </row>
     <row r="4" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C4" s="150"/>
+      <c r="C4" s="148"/>
       <c r="D4" s="86"/>
       <c r="E4" s="86"/>
-      <c r="F4" s="150" t="s">
-        <v>192</v>
+      <c r="F4" s="148" t="s">
+        <v>189</v>
       </c>
       <c r="G4" s="87" t="s">
         <v>111</v>
       </c>
       <c r="H4" s="88"/>
-      <c r="I4" s="149"/>
+      <c r="I4" s="147"/>
       <c r="J4" s="86"/>
     </row>
     <row r="5" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C5" s="149"/>
+      <c r="C5" s="147"/>
       <c r="D5" s="86"/>
       <c r="E5" s="86"/>
-      <c r="F5" s="149"/>
+      <c r="F5" s="147"/>
       <c r="G5" s="90" t="s">
         <v>118</v>
       </c>
       <c r="H5" s="86"/>
-      <c r="I5" s="149"/>
+      <c r="I5" s="147"/>
       <c r="J5" s="86"/>
     </row>
     <row r="6" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C6" s="243"/>
-      <c r="D6" s="244" t="s">
-        <v>327</v>
+      <c r="C6" s="239"/>
+      <c r="D6" s="240" t="s">
+        <v>320</v>
       </c>
       <c r="E6" s="86"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="151"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="149"/>
       <c r="H6" s="86"/>
-      <c r="I6" s="149"/>
+      <c r="I6" s="147"/>
       <c r="J6" s="86"/>
     </row>
     <row r="7" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C7" s="155" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="156" t="s">
-        <v>263</v>
-      </c>
-      <c r="E7" s="212"/>
-      <c r="F7" s="245"/>
-      <c r="G7" s="246"/>
-      <c r="H7" s="212"/>
-      <c r="I7" s="245"/>
-      <c r="J7" s="212"/>
+      <c r="C7" s="153" t="s">
+        <v>188</v>
+      </c>
+      <c r="D7" s="154" t="s">
+        <v>260</v>
+      </c>
+      <c r="E7" s="210"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="210"/>
+      <c r="I7" s="241"/>
+      <c r="J7" s="210"/>
     </row>
     <row r="8" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C8" s="155" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="156" t="s">
-        <v>296</v>
+      <c r="C8" s="153" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="154" t="s">
+        <v>289</v>
       </c>
       <c r="E8" s="86"/>
-      <c r="F8" s="152" t="s">
-        <v>191</v>
-      </c>
-      <c r="G8" s="242" t="s">
+      <c r="F8" s="150" t="s">
+        <v>188</v>
+      </c>
+      <c r="G8" s="238" t="s">
         <v>164</v>
       </c>
       <c r="H8" s="98"/>
-      <c r="I8" s="152"/>
+      <c r="I8" s="150"/>
       <c r="J8" s="98"/>
       <c r="N8" s="82"/>
     </row>
     <row r="9" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C9" s="337" t="s">
+      <c r="C9" s="328" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="226" t="s">
+        <v>290</v>
+      </c>
+      <c r="E9" s="86"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="152" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="86"/>
+      <c r="I9" s="147"/>
+      <c r="J9" s="86"/>
+    </row>
+    <row r="10" spans="3:14" ht="20.100000000000001" customHeight="1">
+      <c r="C10" s="156" t="s">
+        <v>291</v>
+      </c>
+      <c r="D10" s="157" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" s="86"/>
+      <c r="F10" s="293"/>
+      <c r="G10" s="294"/>
+      <c r="H10" s="150"/>
+      <c r="I10" s="147"/>
+      <c r="J10" s="86"/>
+    </row>
+    <row r="11" spans="3:14" ht="20.100000000000001" customHeight="1">
+      <c r="C11" s="153" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="244" t="s">
+        <v>293</v>
+      </c>
+      <c r="E11" s="86"/>
+      <c r="F11" s="171"/>
+      <c r="G11" s="307" t="s">
+        <v>270</v>
+      </c>
+      <c r="H11" s="150"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="115" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="3:14" ht="20.100000000000001" customHeight="1">
+      <c r="C12" s="243" t="s">
+        <v>255</v>
+      </c>
+      <c r="D12" s="303" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" s="210"/>
+      <c r="F12" s="171" t="s">
+        <v>190</v>
+      </c>
+      <c r="G12" s="172" t="s">
+        <v>213</v>
+      </c>
+      <c r="H12" s="245"/>
+      <c r="I12" s="246" t="s">
+        <v>191</v>
+      </c>
+      <c r="J12" s="247" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="3:14" ht="20.100000000000001" customHeight="1">
+      <c r="C13" s="153" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="228" t="s">
+      <c r="D13" s="154" t="s">
+        <v>294</v>
+      </c>
+      <c r="E13" s="86"/>
+      <c r="F13" s="171" t="s">
+        <v>188</v>
+      </c>
+      <c r="G13" s="174" t="s">
+        <v>232</v>
+      </c>
+      <c r="H13" s="150"/>
+      <c r="I13" s="160" t="s">
+        <v>188</v>
+      </c>
+      <c r="J13" s="161" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="3:14" ht="20.100000000000001" customHeight="1">
+      <c r="C14" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="154" t="s">
+        <v>295</v>
+      </c>
+      <c r="E14" s="86"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="174" t="s">
+        <v>170</v>
+      </c>
+      <c r="H14" s="150"/>
+      <c r="I14" s="160"/>
+      <c r="J14" s="161" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="3:14" ht="20.100000000000001" customHeight="1">
+      <c r="C15" s="156" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="157" t="s">
+        <v>296</v>
+      </c>
+      <c r="E15" s="86"/>
+      <c r="F15" s="171"/>
+      <c r="G15" s="174" t="s">
+        <v>252</v>
+      </c>
+      <c r="H15" s="150"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="161" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="3:14" ht="20.100000000000001" customHeight="1">
+      <c r="C16" s="243" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="244" t="s">
         <v>297</v>
       </c>
-      <c r="E9" s="86"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="154" t="s">
-        <v>172</v>
-      </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="149"/>
-      <c r="J9" s="86"/>
-    </row>
-    <row r="10" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C10" s="158" t="s">
+      <c r="E16" s="210"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="258" t="s">
+        <v>253</v>
+      </c>
+      <c r="H16" s="245"/>
+      <c r="I16" s="248"/>
+      <c r="J16" s="249" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C17" s="250"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="176" t="s">
+        <v>254</v>
+      </c>
+      <c r="H17" s="150"/>
+      <c r="I17" s="162" t="s">
+        <v>188</v>
+      </c>
+      <c r="J17" s="163" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C18" s="156" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="157" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="159" t="s">
+      <c r="E18" s="86"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="176" t="s">
+        <v>185</v>
+      </c>
+      <c r="H18" s="150"/>
+      <c r="I18" s="147"/>
+      <c r="J18" s="150"/>
+    </row>
+    <row r="19" spans="3:10" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="C19" s="153" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" s="154" t="s">
         <v>299</v>
       </c>
-      <c r="E10" s="86"/>
-      <c r="F10" s="300"/>
-      <c r="G10" s="301"/>
-      <c r="H10" s="152"/>
-      <c r="I10" s="149"/>
-      <c r="J10" s="86"/>
-    </row>
-    <row r="11" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C11" s="155" t="s">
-        <v>204</v>
-      </c>
-      <c r="D11" s="248" t="s">
+      <c r="E19" s="86"/>
+      <c r="F19" s="171" t="s">
+        <v>189</v>
+      </c>
+      <c r="G19" s="179" t="s">
+        <v>268</v>
+      </c>
+      <c r="H19" s="150"/>
+      <c r="I19" s="150"/>
+      <c r="J19" s="150"/>
+    </row>
+    <row r="20" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C20" s="338" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="164" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="86"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="150"/>
+      <c r="J20" s="150"/>
+    </row>
+    <row r="21" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C21" s="153" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" s="165" t="s">
         <v>300</v>
       </c>
-      <c r="E11" s="86"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="316" t="s">
-        <v>277</v>
-      </c>
-      <c r="H11" s="152"/>
-      <c r="I11" s="160"/>
-      <c r="J11" s="115" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="12" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C12" s="247" t="s">
-        <v>258</v>
-      </c>
-      <c r="D12" s="312" t="s">
-        <v>264</v>
-      </c>
-      <c r="E12" s="212"/>
-      <c r="F12" s="173" t="s">
-        <v>193</v>
-      </c>
-      <c r="G12" s="174" t="s">
-        <v>216</v>
-      </c>
-      <c r="H12" s="249"/>
-      <c r="I12" s="250" t="s">
-        <v>194</v>
-      </c>
-      <c r="J12" s="251" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C13" s="155" t="s">
-        <v>195</v>
-      </c>
-      <c r="D13" s="156" t="s">
+      <c r="E21" s="86"/>
+      <c r="F21" s="150"/>
+      <c r="G21" s="150"/>
+      <c r="H21" s="150"/>
+      <c r="I21" s="150"/>
+      <c r="J21" s="150"/>
+    </row>
+    <row r="22" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C22" s="243" t="s">
+        <v>220</v>
+      </c>
+      <c r="D22" s="253" t="s">
         <v>301</v>
       </c>
-      <c r="E13" s="86"/>
-      <c r="F13" s="173" t="s">
-        <v>191</v>
-      </c>
-      <c r="G13" s="176" t="s">
-        <v>235</v>
-      </c>
-      <c r="H13" s="152"/>
-      <c r="I13" s="162" t="s">
-        <v>191</v>
-      </c>
-      <c r="J13" s="163" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="14" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C14" s="155" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" s="156" t="s">
-        <v>302</v>
-      </c>
-      <c r="E14" s="86"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="176" t="s">
-        <v>170</v>
-      </c>
-      <c r="H14" s="152"/>
-      <c r="I14" s="162"/>
-      <c r="J14" s="163" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="15" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C15" s="158" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E15" s="86"/>
-      <c r="F15" s="173"/>
-      <c r="G15" s="176" t="s">
-        <v>255</v>
-      </c>
-      <c r="H15" s="152"/>
-      <c r="I15" s="162"/>
-      <c r="J15" s="163" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="16" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C16" s="247" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="248" t="s">
-        <v>304</v>
-      </c>
-      <c r="E16" s="212"/>
-      <c r="F16" s="173"/>
-      <c r="G16" s="262" t="s">
-        <v>256</v>
-      </c>
-      <c r="H16" s="249"/>
-      <c r="I16" s="252"/>
-      <c r="J16" s="253" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C17" s="254"/>
-      <c r="D17" s="255"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="261"/>
-      <c r="G17" s="178" t="s">
-        <v>257</v>
-      </c>
-      <c r="H17" s="152"/>
-      <c r="I17" s="164" t="s">
-        <v>191</v>
-      </c>
-      <c r="J17" s="165" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C18" s="158" t="s">
-        <v>208</v>
-      </c>
-      <c r="D18" s="159" t="s">
-        <v>305</v>
-      </c>
-      <c r="E18" s="86"/>
-      <c r="F18" s="185"/>
-      <c r="G18" s="178" t="s">
-        <v>188</v>
-      </c>
-      <c r="H18" s="152"/>
-      <c r="I18" s="149"/>
-      <c r="J18" s="152"/>
-    </row>
-    <row r="19" spans="3:10" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="C19" s="155" t="s">
-        <v>222</v>
-      </c>
-      <c r="D19" s="156" t="s">
-        <v>306</v>
-      </c>
-      <c r="E19" s="86"/>
-      <c r="F19" s="173" t="s">
-        <v>192</v>
-      </c>
-      <c r="G19" s="181" t="s">
-        <v>275</v>
-      </c>
-      <c r="H19" s="152"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="152"/>
-    </row>
-    <row r="20" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C20" s="155" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="166" t="s">
-        <v>288</v>
-      </c>
-      <c r="E20" s="86"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152"/>
-      <c r="H20" s="152"/>
-      <c r="I20" s="152"/>
-      <c r="J20" s="152"/>
-    </row>
-    <row r="21" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C21" s="155" t="s">
-        <v>194</v>
-      </c>
-      <c r="D21" s="167" t="s">
-        <v>307</v>
-      </c>
-      <c r="E21" s="86"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="152"/>
-      <c r="I21" s="152"/>
-      <c r="J21" s="152"/>
-    </row>
-    <row r="22" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C22" s="247" t="s">
-        <v>223</v>
-      </c>
-      <c r="D22" s="257" t="s">
-        <v>308</v>
-      </c>
-      <c r="E22" s="212"/>
-      <c r="F22" s="249"/>
-      <c r="G22" s="249"/>
-      <c r="H22" s="212"/>
-      <c r="I22" s="245"/>
-      <c r="J22" s="212"/>
+      <c r="E22" s="210"/>
+      <c r="F22" s="245"/>
+      <c r="G22" s="245"/>
+      <c r="H22" s="210"/>
+      <c r="I22" s="241"/>
+      <c r="J22" s="210"/>
     </row>
     <row r="23" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C23" s="155"/>
-      <c r="D23" s="256" t="s">
+      <c r="C23" s="153"/>
+      <c r="D23" s="252" t="s">
         <v>113</v>
       </c>
       <c r="E23" s="86"/>
-      <c r="F23" s="149"/>
+      <c r="F23" s="147"/>
       <c r="G23" s="86"/>
       <c r="H23" s="86"/>
-      <c r="I23" s="149"/>
+      <c r="I23" s="147"/>
       <c r="J23" s="86"/>
     </row>
     <row r="24" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C24" s="155" t="s">
-        <v>214</v>
-      </c>
-      <c r="D24" s="313" t="s">
-        <v>265</v>
+      <c r="C24" s="153" t="s">
+        <v>211</v>
+      </c>
+      <c r="D24" s="304" t="s">
+        <v>262</v>
       </c>
       <c r="E24" s="86"/>
-      <c r="F24" s="152"/>
-      <c r="G24" s="152"/>
+      <c r="F24" s="150"/>
+      <c r="G24" s="150"/>
       <c r="H24" s="86"/>
-      <c r="I24" s="149"/>
+      <c r="I24" s="147"/>
       <c r="J24" s="86"/>
     </row>
     <row r="25" spans="3:10" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="C25" s="155" t="s">
-        <v>224</v>
-      </c>
-      <c r="D25" s="168" t="s">
+      <c r="C25" s="153" t="s">
+        <v>221</v>
+      </c>
+      <c r="D25" s="166" t="s">
+        <v>302</v>
+      </c>
+      <c r="E25" s="167"/>
+      <c r="F25" s="168" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="155" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25" s="86"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="86"/>
+    </row>
+    <row r="26" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C26" s="153" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="154" t="s">
+        <v>303</v>
+      </c>
+      <c r="E26" s="86"/>
+      <c r="F26" s="150"/>
+      <c r="G26" s="169"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="147"/>
+      <c r="J26" s="86"/>
+    </row>
+    <row r="27" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C27" s="243" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" s="244" t="s">
+        <v>305</v>
+      </c>
+      <c r="E27" s="210"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="210"/>
+      <c r="I27" s="241"/>
+      <c r="J27" s="210"/>
+    </row>
+    <row r="28" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C28" s="151"/>
+      <c r="D28" s="254" t="s">
+        <v>304</v>
+      </c>
+      <c r="E28" s="167"/>
+      <c r="F28" s="168" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="155" t="s">
+        <v>168</v>
+      </c>
+      <c r="H28" s="86"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="86"/>
+    </row>
+    <row r="29" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C29" s="153" t="s">
+        <v>206</v>
+      </c>
+      <c r="D29" s="254" t="s">
+        <v>263</v>
+      </c>
+      <c r="E29" s="86"/>
+      <c r="F29" s="150"/>
+      <c r="G29" s="150"/>
+      <c r="H29" s="150"/>
+      <c r="I29" s="150"/>
+      <c r="J29" s="150"/>
+    </row>
+    <row r="30" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C30" s="153" t="s">
+        <v>207</v>
+      </c>
+      <c r="D30" s="154" t="s">
+        <v>306</v>
+      </c>
+      <c r="E30" s="86"/>
+      <c r="F30" s="150"/>
+      <c r="G30" s="150"/>
+      <c r="H30" s="150"/>
+      <c r="I30" s="147"/>
+      <c r="J30" s="86"/>
+    </row>
+    <row r="31" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C31" s="153"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="171"/>
+      <c r="G31" s="307" t="s">
+        <v>269</v>
+      </c>
+      <c r="H31" s="150"/>
+      <c r="I31" s="170"/>
+      <c r="J31" s="115" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C32" s="256"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="210"/>
+      <c r="F32" s="171" t="s">
+        <v>190</v>
+      </c>
+      <c r="G32" s="339" t="s">
+        <v>213</v>
+      </c>
+      <c r="H32" s="245"/>
+      <c r="I32" s="248" t="s">
+        <v>191</v>
+      </c>
+      <c r="J32" s="247" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C33" s="153" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="154" t="s">
+        <v>307</v>
+      </c>
+      <c r="E33" s="86"/>
+      <c r="F33" s="171" t="s">
+        <v>188</v>
+      </c>
+      <c r="G33" s="179" t="s">
+        <v>280</v>
+      </c>
+      <c r="H33" s="150"/>
+      <c r="I33" s="255" t="s">
+        <v>188</v>
+      </c>
+      <c r="J33" s="161" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C34" s="151"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="171" t="s">
+        <v>195</v>
+      </c>
+      <c r="G34" s="179" t="s">
+        <v>275</v>
+      </c>
+      <c r="H34" s="150"/>
+      <c r="I34" s="160"/>
+      <c r="J34" s="173"/>
+    </row>
+    <row r="35" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C35" s="153" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" s="154" t="s">
+        <v>308</v>
+      </c>
+      <c r="E35" s="86"/>
+      <c r="F35" s="171" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" s="261" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="150"/>
+      <c r="I35" s="160"/>
+      <c r="J35" s="161" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C36" s="151"/>
+      <c r="D36" s="154"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="171"/>
+      <c r="G36" s="179" t="s">
+        <v>276</v>
+      </c>
+      <c r="H36" s="86"/>
+      <c r="I36" s="160"/>
+      <c r="J36" s="173"/>
+    </row>
+    <row r="37" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C37" s="153" t="s">
+        <v>198</v>
+      </c>
+      <c r="D37" s="154" t="s">
         <v>309</v>
       </c>
-      <c r="E25" s="169"/>
-      <c r="F25" s="170" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="157" t="s">
-        <v>169</v>
-      </c>
-      <c r="H25" s="86"/>
-      <c r="I25" s="149"/>
-      <c r="J25" s="86"/>
-    </row>
-    <row r="26" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C26" s="155" t="s">
+      <c r="E37" s="86"/>
+      <c r="F37" s="171"/>
+      <c r="G37" s="177" t="s">
+        <v>277</v>
+      </c>
+      <c r="H37" s="86"/>
+      <c r="I37" s="175"/>
+      <c r="J37" s="161" t="s">
+        <v>235</v>
+      </c>
+      <c r="O37" s="174"/>
+    </row>
+    <row r="38" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C38" s="243" t="s">
         <v>209</v>
       </c>
-      <c r="D26" s="156" t="s">
+      <c r="D38" s="244" t="s">
         <v>310</v>
       </c>
-      <c r="E26" s="86"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="149"/>
-      <c r="J26" s="86"/>
-    </row>
-    <row r="27" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C27" s="247" t="s">
-        <v>196</v>
-      </c>
-      <c r="D27" s="248" t="s">
-        <v>312</v>
-      </c>
-      <c r="E27" s="212"/>
-      <c r="F27" s="249"/>
-      <c r="G27" s="249"/>
-      <c r="H27" s="212"/>
-      <c r="I27" s="245"/>
-      <c r="J27" s="212"/>
-    </row>
-    <row r="28" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C28" s="153"/>
-      <c r="D28" s="258" t="s">
-        <v>311</v>
-      </c>
-      <c r="E28" s="169"/>
-      <c r="F28" s="170" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="157" t="s">
-        <v>168</v>
-      </c>
-      <c r="H28" s="86"/>
-      <c r="I28" s="149"/>
-      <c r="J28" s="86"/>
-    </row>
-    <row r="29" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C29" s="155" t="s">
-        <v>209</v>
-      </c>
-      <c r="D29" s="258" t="s">
-        <v>266</v>
-      </c>
-      <c r="E29" s="86"/>
-      <c r="F29" s="152"/>
-      <c r="G29" s="152"/>
-      <c r="H29" s="152"/>
-      <c r="I29" s="152"/>
-      <c r="J29" s="152"/>
-    </row>
-    <row r="30" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C30" s="155" t="s">
-        <v>210</v>
-      </c>
-      <c r="D30" s="156" t="s">
-        <v>313</v>
-      </c>
-      <c r="E30" s="86"/>
-      <c r="F30" s="152"/>
-      <c r="G30" s="152"/>
-      <c r="H30" s="152"/>
-      <c r="I30" s="149"/>
-      <c r="J30" s="86"/>
-    </row>
-    <row r="31" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C31" s="155"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="173"/>
-      <c r="G31" s="316" t="s">
-        <v>276</v>
-      </c>
-      <c r="H31" s="152"/>
-      <c r="I31" s="172"/>
-      <c r="J31" s="115" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C32" s="260"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="212"/>
-      <c r="F32" s="173" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="174" t="s">
-        <v>216</v>
-      </c>
-      <c r="H32" s="249"/>
-      <c r="I32" s="252" t="s">
-        <v>194</v>
-      </c>
-      <c r="J32" s="251" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C33" s="155" t="s">
-        <v>197</v>
-      </c>
-      <c r="D33" s="156" t="s">
-        <v>314</v>
-      </c>
-      <c r="E33" s="86"/>
-      <c r="F33" s="173" t="s">
-        <v>191</v>
-      </c>
-      <c r="G33" s="181" t="s">
-        <v>287</v>
-      </c>
-      <c r="H33" s="152"/>
-      <c r="I33" s="259" t="s">
-        <v>191</v>
-      </c>
-      <c r="J33" s="163" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="34" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C34" s="153"/>
-      <c r="D34" s="156"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="173" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="181" t="s">
-        <v>282</v>
-      </c>
-      <c r="H34" s="152"/>
-      <c r="I34" s="162"/>
-      <c r="J34" s="175"/>
-    </row>
-    <row r="35" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C35" s="155" t="s">
-        <v>211</v>
-      </c>
-      <c r="D35" s="156" t="s">
-        <v>315</v>
-      </c>
-      <c r="E35" s="86"/>
-      <c r="F35" s="173" t="s">
-        <v>192</v>
-      </c>
-      <c r="G35" s="265" t="s">
-        <v>167</v>
-      </c>
-      <c r="H35" s="152"/>
-      <c r="I35" s="162"/>
-      <c r="J35" s="163" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C36" s="153"/>
-      <c r="D36" s="156"/>
-      <c r="E36" s="86"/>
-      <c r="F36" s="173"/>
-      <c r="G36" s="181" t="s">
-        <v>283</v>
-      </c>
-      <c r="H36" s="86"/>
-      <c r="I36" s="162"/>
-      <c r="J36" s="175"/>
-    </row>
-    <row r="37" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C37" s="155" t="s">
-        <v>201</v>
-      </c>
-      <c r="D37" s="156" t="s">
-        <v>316</v>
-      </c>
-      <c r="E37" s="86"/>
-      <c r="F37" s="173"/>
-      <c r="G37" s="179" t="s">
-        <v>284</v>
-      </c>
-      <c r="H37" s="86"/>
-      <c r="I37" s="177"/>
-      <c r="J37" s="163" t="s">
-        <v>238</v>
-      </c>
-      <c r="O37" s="176"/>
-    </row>
-    <row r="38" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C38" s="247" t="s">
-        <v>212</v>
-      </c>
-      <c r="D38" s="248" t="s">
-        <v>317</v>
-      </c>
-      <c r="E38" s="212"/>
-      <c r="F38" s="261"/>
-      <c r="G38" s="191"/>
-      <c r="H38" s="212"/>
-      <c r="I38" s="263"/>
-      <c r="J38" s="264"/>
+      <c r="E38" s="210"/>
+      <c r="F38" s="257"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="210"/>
+      <c r="I38" s="259"/>
+      <c r="J38" s="260"/>
     </row>
     <row r="39" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C39" s="153"/>
+      <c r="C39" s="151"/>
       <c r="D39" s="110"/>
       <c r="E39" s="86"/>
-      <c r="F39" s="185"/>
-      <c r="G39" s="181" t="s">
-        <v>285</v>
+      <c r="F39" s="183"/>
+      <c r="G39" s="179" t="s">
+        <v>278</v>
       </c>
       <c r="H39" s="86"/>
-      <c r="I39" s="177"/>
-      <c r="J39" s="163" t="s">
-        <v>187</v>
+      <c r="I39" s="175"/>
+      <c r="J39" s="161" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C40" s="155" t="s">
-        <v>205</v>
-      </c>
-      <c r="D40" s="156" t="s">
-        <v>318</v>
+      <c r="C40" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="D40" s="154" t="s">
+        <v>311</v>
       </c>
       <c r="E40" s="86"/>
-      <c r="F40" s="173"/>
-      <c r="G40" s="178"/>
-      <c r="H40" s="152"/>
-      <c r="I40" s="177"/>
-      <c r="J40" s="175"/>
+      <c r="F40" s="171"/>
+      <c r="G40" s="176"/>
+      <c r="H40" s="150"/>
+      <c r="I40" s="175"/>
+      <c r="J40" s="173"/>
     </row>
     <row r="41" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C41" s="155" t="s">
-        <v>213</v>
-      </c>
-      <c r="D41" s="156" t="s">
-        <v>319</v>
+      <c r="C41" s="153" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" s="154" t="s">
+        <v>312</v>
       </c>
       <c r="E41" s="86"/>
-      <c r="F41" s="173" t="s">
-        <v>192</v>
-      </c>
-      <c r="G41" s="317" t="s">
-        <v>286</v>
-      </c>
-      <c r="H41" s="151"/>
-      <c r="I41" s="180" t="s">
-        <v>192</v>
-      </c>
-      <c r="J41" s="165" t="s">
-        <v>254</v>
+      <c r="F41" s="171" t="s">
+        <v>189</v>
+      </c>
+      <c r="G41" s="308" t="s">
+        <v>279</v>
+      </c>
+      <c r="H41" s="149"/>
+      <c r="I41" s="178" t="s">
+        <v>189</v>
+      </c>
+      <c r="J41" s="163" t="s">
+        <v>251</v>
       </c>
       <c r="L41" s="83"/>
     </row>
     <row r="42" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C42" s="155" t="s">
-        <v>204</v>
-      </c>
-      <c r="D42" s="156" t="s">
-        <v>320</v>
+      <c r="C42" s="153" t="s">
+        <v>201</v>
+      </c>
+      <c r="D42" s="154" t="s">
+        <v>313</v>
       </c>
       <c r="E42" s="86"/>
-      <c r="F42" s="321"/>
-      <c r="G42" s="322"/>
-      <c r="H42" s="182"/>
-      <c r="I42" s="183"/>
+      <c r="F42" s="312"/>
+      <c r="G42" s="313"/>
+      <c r="H42" s="180"/>
+      <c r="I42" s="181"/>
       <c r="J42" s="86"/>
       <c r="L42" s="83"/>
     </row>
     <row r="43" spans="3:15" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="C43" s="260"/>
-      <c r="D43" s="339"/>
-      <c r="E43" s="212"/>
-      <c r="F43" s="323"/>
-      <c r="G43" s="324"/>
-      <c r="H43" s="182"/>
-      <c r="I43" s="149"/>
+      <c r="C43" s="256"/>
+      <c r="D43" s="330"/>
+      <c r="E43" s="210"/>
+      <c r="F43" s="314"/>
+      <c r="G43" s="315"/>
+      <c r="H43" s="180"/>
+      <c r="I43" s="147"/>
       <c r="J43" s="86"/>
       <c r="L43" s="83"/>
     </row>
     <row r="44" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C44" s="158" t="s">
-        <v>214</v>
-      </c>
-      <c r="D44" s="318" t="s">
-        <v>321</v>
+      <c r="C44" s="156" t="s">
+        <v>211</v>
+      </c>
+      <c r="D44" s="309" t="s">
+        <v>314</v>
       </c>
       <c r="E44" s="86"/>
-      <c r="F44" s="321"/>
-      <c r="G44" s="322"/>
-      <c r="H44" s="182"/>
-      <c r="I44" s="184"/>
+      <c r="F44" s="312"/>
+      <c r="G44" s="313"/>
+      <c r="H44" s="180"/>
+      <c r="I44" s="182"/>
       <c r="J44" s="124" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L44" s="83"/>
     </row>
     <row r="45" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C45" s="155" t="s">
+      <c r="C45" s="153" t="s">
+        <v>212</v>
+      </c>
+      <c r="D45" s="310" t="s">
+        <v>315</v>
+      </c>
+      <c r="E45" s="86"/>
+      <c r="F45" s="316"/>
+      <c r="G45" s="317"/>
+      <c r="H45" s="180"/>
+      <c r="I45" s="183"/>
+      <c r="J45" s="288" t="s">
+        <v>236</v>
+      </c>
+      <c r="L45" s="83"/>
+    </row>
+    <row r="46" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C46" s="153" t="s">
+        <v>197</v>
+      </c>
+      <c r="D46" s="310" t="s">
+        <v>316</v>
+      </c>
+      <c r="E46" s="86"/>
+      <c r="F46" s="318"/>
+      <c r="G46" s="313"/>
+      <c r="H46" s="180"/>
+      <c r="I46" s="184"/>
+      <c r="J46" s="185"/>
+    </row>
+    <row r="47" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C47" s="153" t="s">
+        <v>199</v>
+      </c>
+      <c r="D47" s="310" t="s">
+        <v>317</v>
+      </c>
+      <c r="E47" s="86"/>
+      <c r="F47" s="319"/>
+      <c r="G47" s="320"/>
+      <c r="H47" s="186"/>
+      <c r="I47" s="187"/>
+      <c r="J47" s="188"/>
+    </row>
+    <row r="48" spans="3:15" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="C48" s="153" t="s">
+        <v>200</v>
+      </c>
+      <c r="D48" s="311" t="s">
+        <v>318</v>
+      </c>
+      <c r="E48" s="86"/>
+      <c r="F48" s="297"/>
+      <c r="G48" s="298"/>
+      <c r="H48" s="186"/>
+      <c r="I48" s="187"/>
+      <c r="J48" s="188"/>
+    </row>
+    <row r="49" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C49" s="262"/>
+      <c r="D49" s="263" t="s">
+        <v>264</v>
+      </c>
+      <c r="E49" s="167" t="s">
+        <v>112</v>
+      </c>
+      <c r="F49" s="295" t="s">
+        <v>112</v>
+      </c>
+      <c r="G49" s="296" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" s="86"/>
+      <c r="I49" s="183"/>
+      <c r="J49" s="131"/>
+    </row>
+    <row r="50" spans="3:10" ht="20.100000000000001" customHeight="1">
+      <c r="C50" s="265"/>
+      <c r="D50" s="266"/>
+      <c r="E50" s="86"/>
+      <c r="F50" s="150" t="s">
+        <v>191</v>
+      </c>
+      <c r="G50" s="191" t="s">
         <v>215</v>
       </c>
-      <c r="D45" s="319" t="s">
-        <v>322</v>
-      </c>
-      <c r="E45" s="86"/>
-      <c r="F45" s="325"/>
-      <c r="G45" s="326"/>
-      <c r="H45" s="182"/>
-      <c r="I45" s="185"/>
-      <c r="J45" s="294" t="s">
-        <v>239</v>
-      </c>
-      <c r="L45" s="83"/>
-    </row>
-    <row r="46" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C46" s="155" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" s="319" t="s">
-        <v>323</v>
-      </c>
-      <c r="E46" s="86"/>
-      <c r="F46" s="327"/>
-      <c r="G46" s="322"/>
-      <c r="H46" s="182"/>
-      <c r="I46" s="186"/>
-      <c r="J46" s="187"/>
-    </row>
-    <row r="47" spans="3:15" ht="20.100000000000001" customHeight="1">
-      <c r="C47" s="155" t="s">
-        <v>202</v>
-      </c>
-      <c r="D47" s="319" t="s">
-        <v>324</v>
-      </c>
-      <c r="E47" s="86"/>
-      <c r="F47" s="328"/>
-      <c r="G47" s="329"/>
-      <c r="H47" s="188"/>
-      <c r="I47" s="189"/>
-      <c r="J47" s="190"/>
-    </row>
-    <row r="48" spans="3:15" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="C48" s="155" t="s">
-        <v>203</v>
-      </c>
-      <c r="D48" s="320" t="s">
-        <v>325</v>
-      </c>
-      <c r="E48" s="86"/>
-      <c r="F48" s="304"/>
-      <c r="G48" s="305"/>
-      <c r="H48" s="188"/>
-      <c r="I48" s="189"/>
-      <c r="J48" s="190"/>
-    </row>
-    <row r="49" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C49" s="266"/>
-      <c r="D49" s="267" t="s">
-        <v>267</v>
-      </c>
-      <c r="E49" s="169" t="s">
-        <v>112</v>
-      </c>
-      <c r="F49" s="302" t="s">
-        <v>112</v>
-      </c>
-      <c r="G49" s="303" t="s">
-        <v>171</v>
-      </c>
-      <c r="H49" s="86"/>
-      <c r="I49" s="185"/>
-      <c r="J49" s="131"/>
-    </row>
-    <row r="50" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C50" s="269"/>
-      <c r="D50" s="270"/>
-      <c r="E50" s="86"/>
-      <c r="F50" s="152" t="s">
-        <v>194</v>
-      </c>
-      <c r="G50" s="193" t="s">
-        <v>218</v>
-      </c>
       <c r="H50" s="86"/>
-      <c r="I50" s="273"/>
-      <c r="J50" s="262"/>
+      <c r="I50" s="267"/>
+      <c r="J50" s="258"/>
     </row>
     <row r="51" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C51" s="149"/>
+      <c r="C51" s="147"/>
       <c r="D51" s="86"/>
       <c r="E51" s="131"/>
-      <c r="F51" s="194" t="s">
-        <v>191</v>
-      </c>
-      <c r="G51" s="195" t="s">
-        <v>278</v>
-      </c>
-      <c r="H51" s="196"/>
-      <c r="I51" s="295"/>
-      <c r="J51" s="296"/>
+      <c r="F51" s="192" t="s">
+        <v>188</v>
+      </c>
+      <c r="G51" s="193" t="s">
+        <v>271</v>
+      </c>
+      <c r="H51" s="194"/>
+      <c r="I51" s="289"/>
+      <c r="J51" s="290"/>
     </row>
     <row r="52" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C52" s="149"/>
+      <c r="C52" s="147"/>
       <c r="D52" s="86"/>
       <c r="E52" s="131"/>
-      <c r="F52" s="185"/>
-      <c r="G52" s="197" t="s">
-        <v>225</v>
-      </c>
-      <c r="H52" s="169" t="s">
+      <c r="F52" s="183"/>
+      <c r="G52" s="195" t="s">
+        <v>222</v>
+      </c>
+      <c r="H52" s="167" t="s">
         <v>112</v>
       </c>
-      <c r="I52" s="309" t="s">
+      <c r="I52" s="301" t="s">
         <v>112</v>
       </c>
-      <c r="J52" s="293" t="s">
+      <c r="J52" s="287" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="53" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C53" s="149"/>
+      <c r="C53" s="147"/>
       <c r="D53" s="86"/>
       <c r="E53" s="131"/>
-      <c r="F53" s="218" t="s">
-        <v>189</v>
-      </c>
-      <c r="G53" s="285"/>
+      <c r="F53" s="216" t="s">
+        <v>186</v>
+      </c>
+      <c r="G53" s="279"/>
       <c r="H53" s="86"/>
-      <c r="I53" s="170"/>
+      <c r="I53" s="168"/>
       <c r="J53" s="86"/>
     </row>
     <row r="54" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C54" s="245"/>
-      <c r="D54" s="212"/>
+      <c r="C54" s="241"/>
+      <c r="D54" s="210"/>
       <c r="E54" s="131"/>
-      <c r="F54" s="198"/>
-      <c r="G54" s="199"/>
+      <c r="F54" s="196"/>
+      <c r="G54" s="197"/>
       <c r="H54" s="86"/>
-      <c r="I54" s="245"/>
-      <c r="J54" s="212"/>
+      <c r="I54" s="241"/>
+      <c r="J54" s="210"/>
     </row>
     <row r="55" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C55" s="149"/>
+      <c r="C55" s="147"/>
       <c r="D55" s="86"/>
       <c r="E55" s="86"/>
-      <c r="F55" s="152" t="s">
-        <v>191</v>
-      </c>
-      <c r="G55" s="192" t="s">
-        <v>217</v>
+      <c r="F55" s="150" t="s">
+        <v>188</v>
+      </c>
+      <c r="G55" s="190" t="s">
+        <v>214</v>
       </c>
       <c r="H55" s="86"/>
-      <c r="I55" s="149"/>
+      <c r="I55" s="147"/>
       <c r="J55" s="86"/>
     </row>
     <row r="56" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C56" s="149"/>
+      <c r="C56" s="147"/>
       <c r="D56" s="86"/>
       <c r="E56" s="86"/>
-      <c r="F56" s="201" t="s">
-        <v>192</v>
-      </c>
-      <c r="G56" s="200" t="s">
-        <v>230</v>
+      <c r="F56" s="199" t="s">
+        <v>189</v>
+      </c>
+      <c r="G56" s="198" t="s">
+        <v>227</v>
       </c>
       <c r="H56" s="101"/>
-      <c r="I56" s="149"/>
-      <c r="J56" s="149"/>
+      <c r="I56" s="147"/>
+      <c r="J56" s="147"/>
     </row>
     <row r="57" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C57" s="245"/>
-      <c r="D57" s="212"/>
-      <c r="E57" s="212"/>
-      <c r="F57" s="286"/>
-      <c r="G57" s="297" t="s">
+      <c r="C57" s="241"/>
+      <c r="D57" s="210"/>
+      <c r="E57" s="210"/>
+      <c r="F57" s="280"/>
+      <c r="G57" s="291" t="s">
         <v>173</v>
       </c>
-      <c r="H57" s="287"/>
-      <c r="I57" s="245"/>
-      <c r="J57" s="245"/>
+      <c r="H57" s="281"/>
+      <c r="I57" s="241"/>
+      <c r="J57" s="241"/>
     </row>
     <row r="58" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C58" s="288"/>
-      <c r="D58" s="215"/>
-      <c r="E58" s="215"/>
-      <c r="F58" s="289"/>
-      <c r="G58" s="290"/>
-      <c r="H58" s="215"/>
-      <c r="I58" s="288"/>
-      <c r="J58" s="215"/>
+      <c r="C58" s="282"/>
+      <c r="D58" s="213"/>
+      <c r="E58" s="213"/>
+      <c r="F58" s="283"/>
+      <c r="G58" s="284"/>
+      <c r="H58" s="213"/>
+      <c r="I58" s="282"/>
+      <c r="J58" s="213"/>
     </row>
     <row r="59" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C59" s="245"/>
-      <c r="D59" s="212"/>
-      <c r="E59" s="212"/>
-      <c r="F59" s="291"/>
-      <c r="G59" s="292"/>
-      <c r="H59" s="216"/>
-      <c r="I59" s="245"/>
-      <c r="J59" s="212"/>
+      <c r="C59" s="241"/>
+      <c r="D59" s="210"/>
+      <c r="E59" s="210"/>
+      <c r="F59" s="285"/>
+      <c r="G59" s="286"/>
+      <c r="H59" s="214"/>
+      <c r="I59" s="241"/>
+      <c r="J59" s="210"/>
     </row>
     <row r="60" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C60" s="149"/>
+      <c r="C60" s="147"/>
       <c r="D60" s="86"/>
       <c r="E60" s="86"/>
-      <c r="F60" s="271" t="s">
-        <v>191</v>
-      </c>
-      <c r="G60" s="272" t="s">
+      <c r="F60" s="350" t="s">
+        <v>188</v>
+      </c>
+      <c r="G60" s="351" t="s">
         <v>103</v>
       </c>
       <c r="H60" s="86"/>
-      <c r="I60" s="149"/>
+      <c r="I60" s="147"/>
       <c r="J60" s="86"/>
     </row>
     <row r="61" spans="3:10" ht="20.100000000000001" customHeight="1">
-      <c r="C61" s="149"/>
+      <c r="C61" s="147"/>
       <c r="D61" s="86"/>
       <c r="E61" s="86"/>
-      <c r="F61" s="149"/>
+      <c r="F61" s="147"/>
       <c r="G61" s="86"/>
       <c r="H61" s="86"/>
-      <c r="I61" s="149"/>
+      <c r="I61" s="147"/>
       <c r="J61" s="86"/>
     </row>
     <row r="62" spans="3:10" ht="20.100000000000001" customHeight="1"/>
@@ -23978,14 +24629,14 @@
       <c r="B2" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="342" t="s">
+      <c r="C2" s="333" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="343"/>
-      <c r="E2" s="342" t="s">
+      <c r="D2" s="334"/>
+      <c r="E2" s="333" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="343"/>
+      <c r="F2" s="334"/>
       <c r="G2" s="73" t="s">
         <v>122</v>
       </c>
@@ -24554,10 +25205,10 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="35.1" customHeight="1">
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="335" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="345">
+      <c r="C3" s="336">
         <f>SUM(F4:R4)</f>
         <v>1648821</v>
       </c>
@@ -24579,8 +25230,8 @@
       </c>
     </row>
     <row r="4" spans="1:19" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B4" s="344"/>
-      <c r="C4" s="345"/>
+      <c r="B4" s="335"/>
+      <c r="C4" s="336"/>
       <c r="F4" s="20">
         <v>856821</v>
       </c>
@@ -24610,10 +25261,10 @@
       <c r="O5" s="21"/>
     </row>
     <row r="6" spans="1:19" ht="35.1" customHeight="1">
-      <c r="B6" s="346" t="s">
+      <c r="B6" s="337" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="345">
+      <c r="C6" s="336">
         <f>SUM(F7:R7)</f>
         <v>1841452</v>
       </c>
@@ -24638,8 +25289,8 @@
     </row>
     <row r="7" spans="1:19" ht="35.1" customHeight="1">
       <c r="A7" s="19"/>
-      <c r="B7" s="346"/>
-      <c r="C7" s="345"/>
+      <c r="B7" s="337"/>
+      <c r="C7" s="336"/>
       <c r="D7" s="19"/>
       <c r="F7" s="20">
         <f>F4</f>
